--- a/test-data-files/TestData.xlsx
+++ b/test-data-files/TestData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Reetanshu Kumar\Documents\GitHub\selenium-restassured-automation\test-data-files\"/>
     </mc:Choice>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Repository</t>
   </si>
@@ -45,12 +45,16 @@
   </si>
   <si>
     <t>Ratings</t>
+  </si>
+  <si>
+    <t>new_Repo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -385,10 +389,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="23.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -421,6 +425,14 @@
       </c>
       <c r="B4" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>4.0</v>
       </c>
     </row>
   </sheetData>
